--- a/Golf Holiday V2.xlsx
+++ b/Golf Holiday V2.xlsx
@@ -7,8 +7,9 @@
     <sheet state="visible" name="Holidays" sheetId="2" r:id="rId6"/>
     <sheet state="visible" name="Matchdays" sheetId="3" r:id="rId7"/>
     <sheet state="visible" name="Matches" sheetId="4" r:id="rId8"/>
-    <sheet state="visible" name="Green Jackets" sheetId="5" r:id="rId9"/>
-    <sheet state="visible" name="Sheet10" sheetId="6" r:id="rId10"/>
+    <sheet state="visible" name="Players" sheetId="5" r:id="rId9"/>
+    <sheet state="visible" name="Green Jackets" sheetId="6" r:id="rId10"/>
+    <sheet state="visible" name="Sheet10" sheetId="7" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName hidden="1" localSheetId="3" name="_xlnm._FilterDatabase">Matches!$A$1:$AF$56</definedName>
@@ -18,17 +19,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="173">
-  <si>
-    <t>Individual/Team Scatter Plot by player</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="200">
   <si>
     <t>Game Type by team results</t>
   </si>
   <si>
-    <t>Click through tabs to see Green Jacket leaderboards from different years</t>
-  </si>
-  <si>
     <t>holiday_id</t>
   </si>
   <si>
@@ -188,190 +183,277 @@
     <t>Green Jacket</t>
   </si>
   <si>
+    <t>C. Peters</t>
+  </si>
+  <si>
+    <t>Running over Cranham in the buggie</t>
+  </si>
+  <si>
+    <t>Miguel Angel Jimenez Academy</t>
+  </si>
+  <si>
+    <t>Pissing on the course in a well</t>
+  </si>
+  <si>
+    <t>Calanova</t>
+  </si>
+  <si>
+    <t>Being sick on the course</t>
+  </si>
+  <si>
+    <t>El Chaparral</t>
+  </si>
+  <si>
+    <t>Missing tee shot again</t>
+  </si>
+  <si>
+    <t>Marbella</t>
+  </si>
+  <si>
+    <t>Brown</t>
+  </si>
+  <si>
+    <t>Shaking the tree</t>
+  </si>
+  <si>
+    <t>La Cala (Asia)</t>
+  </si>
+  <si>
+    <t>Chair in sea, hit house</t>
+  </si>
+  <si>
+    <t>Kaya Belek</t>
+  </si>
+  <si>
+    <t>Smashing everything on the table</t>
+  </si>
+  <si>
+    <t>Carya</t>
+  </si>
+  <si>
+    <t>Mulligan</t>
+  </si>
+  <si>
+    <t>Javelining club down the fairway and forgetting about it with it stuck in the ground</t>
+  </si>
+  <si>
+    <t>Montgomerie</t>
+  </si>
+  <si>
+    <t>Disobeying cabbie</t>
+  </si>
+  <si>
+    <t>match_id</t>
+  </si>
+  <si>
+    <t>player_a</t>
+  </si>
+  <si>
+    <t>player_b</t>
+  </si>
+  <si>
+    <t>player_c</t>
+  </si>
+  <si>
+    <t>player_d</t>
+  </si>
+  <si>
+    <t>team_a</t>
+  </si>
+  <si>
+    <t>team_b</t>
+  </si>
+  <si>
+    <t>team_c</t>
+  </si>
+  <si>
+    <t>team_d</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>captain_europe</t>
+  </si>
+  <si>
+    <t>captain_usa</t>
+  </si>
+  <si>
+    <t>points_a</t>
+  </si>
+  <si>
+    <t>points_b</t>
+  </si>
+  <si>
+    <t>points_c</t>
+  </si>
+  <si>
+    <t>points_d</t>
+  </si>
+  <si>
+    <t>chip_in_a</t>
+  </si>
+  <si>
+    <t>chip_in_b</t>
+  </si>
+  <si>
+    <t>chip_in_c</t>
+  </si>
+  <si>
+    <t>chip_in_d</t>
+  </si>
+  <si>
+    <t>birdie_a</t>
+  </si>
+  <si>
+    <t>birdie_b</t>
+  </si>
+  <si>
+    <t>birdie_c</t>
+  </si>
+  <si>
+    <t>birdie_d</t>
+  </si>
+  <si>
+    <t>4&amp;3</t>
+  </si>
+  <si>
+    <t>3&amp;2</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>5&amp;3</t>
+  </si>
+  <si>
+    <t>5.5-7</t>
+  </si>
+  <si>
+    <t>7&amp;5</t>
+  </si>
+  <si>
+    <t>2&amp;1</t>
+  </si>
+  <si>
+    <t>2UP</t>
+  </si>
+  <si>
+    <t>Tie</t>
+  </si>
+  <si>
+    <t>A/S</t>
+  </si>
+  <si>
+    <t>6&amp;4</t>
+  </si>
+  <si>
+    <t>1UP</t>
+  </si>
+  <si>
+    <t>5&amp;4</t>
+  </si>
+  <si>
+    <t>4&amp;2</t>
+  </si>
+  <si>
+    <t>J. Barker</t>
+  </si>
+  <si>
+    <t>3&amp;1</t>
+  </si>
+  <si>
+    <t>6&amp;5</t>
+  </si>
+  <si>
+    <t>player_id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>first_name</t>
+  </si>
+  <si>
+    <t>last_name</t>
+  </si>
+  <si>
+    <t>attending</t>
+  </si>
+  <si>
+    <t>handicap_1</t>
+  </si>
+  <si>
+    <t>handicap_2</t>
+  </si>
+  <si>
+    <t>handicap_3</t>
+  </si>
+  <si>
+    <t>handicap_4</t>
+  </si>
+  <si>
+    <t>Witt</t>
+  </si>
+  <si>
+    <t>Cameron</t>
+  </si>
+  <si>
+    <t>Daniel</t>
+  </si>
+  <si>
+    <t>Gregory</t>
+  </si>
+  <si>
+    <t>Alexander</t>
+  </si>
+  <si>
+    <t>Simon</t>
+  </si>
+  <si>
+    <t>Barker</t>
+  </si>
+  <si>
+    <t>Michael</t>
+  </si>
+  <si>
+    <t>Callum</t>
+  </si>
+  <si>
     <t>Peters</t>
   </si>
   <si>
-    <t>Running over Cranham in the buggie</t>
-  </si>
-  <si>
-    <t>Miguel Angel Jimenez Academy</t>
-  </si>
-  <si>
-    <t>Pissing on the course in a well</t>
-  </si>
-  <si>
-    <t>Calanova</t>
-  </si>
-  <si>
-    <t>Being sick on the course</t>
-  </si>
-  <si>
-    <t>El Chaparral</t>
-  </si>
-  <si>
-    <t>Missing tee shot again</t>
-  </si>
-  <si>
-    <t>Marbella</t>
-  </si>
-  <si>
-    <t>Brown</t>
-  </si>
-  <si>
-    <t>Shaking the tree</t>
-  </si>
-  <si>
-    <t>La Cala (Asia)</t>
-  </si>
-  <si>
-    <t>Chair in sea, hit house</t>
-  </si>
-  <si>
-    <t>Kaya Belek</t>
-  </si>
-  <si>
-    <t>Smashing everything on the table</t>
-  </si>
-  <si>
-    <t>Carya</t>
-  </si>
-  <si>
-    <t>Mulligan</t>
-  </si>
-  <si>
-    <t>Javelining club down the fairway and forgetting about it with it stuck in the ground</t>
-  </si>
-  <si>
-    <t>Montgomerie</t>
-  </si>
-  <si>
-    <t>Disobeying cabbie</t>
-  </si>
-  <si>
-    <t>match_id</t>
-  </si>
-  <si>
-    <t>player_a</t>
-  </si>
-  <si>
-    <t>player_b</t>
-  </si>
-  <si>
-    <t>player_c</t>
-  </si>
-  <si>
-    <t>player_d</t>
-  </si>
-  <si>
-    <t>team_a</t>
-  </si>
-  <si>
-    <t>team_b</t>
-  </si>
-  <si>
-    <t>team_c</t>
-  </si>
-  <si>
-    <t>team_d</t>
-  </si>
-  <si>
-    <t>Result</t>
-  </si>
-  <si>
-    <t>Score</t>
-  </si>
-  <si>
-    <t>captain_europe</t>
-  </si>
-  <si>
-    <t>captain_usa</t>
-  </si>
-  <si>
-    <t>points_a</t>
-  </si>
-  <si>
-    <t>points_b</t>
-  </si>
-  <si>
-    <t>points_c</t>
-  </si>
-  <si>
-    <t>points_d</t>
-  </si>
-  <si>
-    <t>chip_in_a</t>
-  </si>
-  <si>
-    <t>chip_in_b</t>
-  </si>
-  <si>
-    <t>chip_in_c</t>
-  </si>
-  <si>
-    <t>chip_in_d</t>
-  </si>
-  <si>
-    <t>birdie_a</t>
-  </si>
-  <si>
-    <t>birdie_b</t>
-  </si>
-  <si>
-    <t>birdie_c</t>
-  </si>
-  <si>
-    <t>birdie_d</t>
-  </si>
-  <si>
-    <t>4&amp;3</t>
-  </si>
-  <si>
-    <t>3&amp;2</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>5&amp;3</t>
-  </si>
-  <si>
-    <t>5.5-7</t>
-  </si>
-  <si>
-    <t>7&amp;5</t>
-  </si>
-  <si>
-    <t>2&amp;1</t>
-  </si>
-  <si>
-    <t>2UP</t>
-  </si>
-  <si>
-    <t>Tie</t>
-  </si>
-  <si>
-    <t>A/S</t>
-  </si>
-  <si>
-    <t>6&amp;4</t>
-  </si>
-  <si>
-    <t>1UP</t>
-  </si>
-  <si>
-    <t>5&amp;4</t>
-  </si>
-  <si>
-    <t>4&amp;2</t>
-  </si>
-  <si>
-    <t>J. Barker</t>
-  </si>
-  <si>
-    <t>3&amp;1</t>
-  </si>
-  <si>
-    <t>6&amp;5</t>
+    <t>Joel</t>
+  </si>
+  <si>
+    <t>Jack</t>
+  </si>
+  <si>
+    <t>Thomas</t>
+  </si>
+  <si>
+    <t>Charlton</t>
+  </si>
+  <si>
+    <t>Skeet</t>
+  </si>
+  <si>
+    <t>Harvey</t>
+  </si>
+  <si>
+    <t>K. Peters</t>
+  </si>
+  <si>
+    <t>Kieran</t>
+  </si>
+  <si>
+    <t>Champion</t>
+  </si>
+  <si>
+    <t>Ollie</t>
   </si>
   <si>
     <t>date</t>
@@ -697,6 +779,10 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -905,19 +991,9 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -934,31 +1010,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2">
@@ -966,28 +1042,28 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="I2" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -995,28 +1071,28 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="H3" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -1024,28 +1100,28 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="I4" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -1053,28 +1129,28 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="I5" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1095,25 +1171,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
@@ -1148,16 +1224,16 @@
         <v>44707.0</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>38</v>
       </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -1175,16 +1251,16 @@
         <v>44708.0</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>39</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>41</v>
       </c>
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
@@ -1204,10 +1280,10 @@
         <v>44708.0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F4" s="9"/>
       <c r="G4" s="10"/>
@@ -1228,10 +1304,10 @@
         <v>44708.0</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
@@ -1251,16 +1327,16 @@
         <v>44709.0</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>42</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>44</v>
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
@@ -1280,16 +1356,16 @@
         <v>44709.0</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
@@ -1309,16 +1385,16 @@
         <v>44710.0</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
@@ -1338,16 +1414,16 @@
         <v>45071.0</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="G9" s="7" t="s">
         <v>49</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>51</v>
       </c>
       <c r="J9" s="8"/>
       <c r="K9" s="9"/>
@@ -1366,16 +1442,16 @@
         <v>45072.0</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="J10" s="8"/>
       <c r="K10" s="6"/>
@@ -1394,16 +1470,16 @@
         <v>45073.0</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="K11" s="9"/>
       <c r="L11" s="9"/>
@@ -1421,16 +1497,16 @@
         <v>45074.0</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="F12" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>57</v>
       </c>
       <c r="J12" s="8"/>
       <c r="K12" s="6"/>
@@ -1449,16 +1525,16 @@
         <v>45546.0</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I13" s="8"/>
       <c r="J13" s="8"/>
@@ -1478,16 +1554,16 @@
         <v>45547.0</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I14" s="8"/>
       <c r="J14" s="8"/>
@@ -1507,16 +1583,16 @@
         <v>45548.0</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I15" s="8"/>
       <c r="J15" s="8"/>
@@ -1536,14 +1612,14 @@
         <v>45549.0</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I16" s="8"/>
       <c r="J16" s="8"/>
@@ -1563,16 +1639,16 @@
         <v>45550.0</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I17" s="8"/>
       <c r="J17" s="8"/>
@@ -1592,16 +1668,16 @@
         <v>45791.0</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I18" s="8"/>
       <c r="J18" s="8"/>
@@ -1621,16 +1697,16 @@
         <v>45792.0</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I19" s="8"/>
     </row>
@@ -1645,16 +1721,16 @@
         <v>45793.0</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21">
@@ -1668,16 +1744,16 @@
         <v>45794.0</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I21" s="8"/>
       <c r="J21" s="8"/>
@@ -4693,100 +4769,100 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="16" t="s">
-        <v>33</v>
-      </c>
       <c r="H1" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="J1" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="K1" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="L1" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="M1" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="N1" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="O1" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="P1" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="Q1" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="P1" s="16" t="s">
+      <c r="R1" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="Q1" s="16" t="s">
+      <c r="S1" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="T1" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="S1" s="16" t="s">
+      <c r="U1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="T1" s="16" t="s">
+      <c r="V1" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="U1" s="16" t="s">
+      <c r="W1" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="V1" s="16" t="s">
+      <c r="X1" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="W1" s="16" t="s">
+      <c r="Y1" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="X1" s="16" t="s">
+      <c r="Z1" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="Y1" s="16" t="s">
+      <c r="AA1" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="Z1" s="16" t="s">
+      <c r="AB1" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="AA1" s="16" t="s">
+      <c r="AC1" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="AB1" s="16" t="s">
+      <c r="AD1" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="AC1" s="16" t="s">
+      <c r="AE1" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="AD1" s="16" t="s">
+      <c r="AF1" s="16" t="s">
         <v>98</v>
-      </c>
-      <c r="AE1" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="AF1" s="16" t="s">
-        <v>100</v>
       </c>
       <c r="AG1" s="16"/>
     </row>
@@ -4822,22 +4898,22 @@
         <v>1.0</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q2" s="1">
         <v>1.0</v>
@@ -4903,22 +4979,22 @@
         <v>1.0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q3" s="1">
         <v>1.0</v>
@@ -4984,28 +5060,28 @@
         <v>1.0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q4" s="1">
         <v>3.0</v>
@@ -5066,22 +5142,22 @@
         <v>1.0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q5" s="1">
         <v>4.0</v>
@@ -5146,34 +5222,34 @@
         <v>2.0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="R6" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="S6" s="17" t="str">
         <f>vlookup($C6,Holidays!$A:$G,6)</f>
@@ -5232,34 +5308,34 @@
         <v>3.0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q7" s="17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R7" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="S7" s="17" t="str">
         <f>vlookup($C7,Holidays!$A:$G,6)</f>
@@ -5321,28 +5397,28 @@
         <v>4.0</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="Q8" s="17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="S8" s="17" t="str">
         <f>vlookup($C8,Holidays!$A:$G,6)</f>
@@ -5401,31 +5477,31 @@
         <v>5.0</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P9" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q9" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="R9" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="Q9" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="R9" s="6" t="s">
-        <v>105</v>
       </c>
       <c r="S9" s="17" t="str">
         <f>vlookup($C9,Holidays!$A:$G,6)</f>
@@ -5484,28 +5560,28 @@
         <v>6.0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="Q10" s="17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="R10" s="22" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="S10" s="17" t="str">
         <f>vlookup($C10,Holidays!$A:$G,6)</f>
@@ -5564,28 +5640,28 @@
         <v>7.0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="Q11" s="17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R11" s="22" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="S11" s="17" t="str">
         <f>vlookup($C11,Holidays!$A:$G,6)</f>
@@ -5644,28 +5720,28 @@
         <v>8.0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="Q12" s="17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="R12" s="22" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="S12" s="17" t="str">
         <f>vlookup($C12,Holidays!$A:$G,6)</f>
@@ -5724,28 +5800,28 @@
         <v>9.0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="Q13" s="17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R13" s="22" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="S13" s="17" t="str">
         <f>vlookup($C13,Holidays!$A:$G,6)</f>
@@ -5804,28 +5880,28 @@
         <v>10.0</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="Q14" s="17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="R14" s="22" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="S14" s="17" t="str">
         <f>vlookup($C14,Holidays!$A:$G,6)</f>
@@ -5887,28 +5963,28 @@
         <v>11.0</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="Q15" s="17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R15" s="22" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="S15" s="17" t="str">
         <f>vlookup($C15,Holidays!$A:$G,6)</f>
@@ -5967,28 +6043,28 @@
         <v>12.0</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="Q16" s="17" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="R16" s="22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="S16" s="17" t="str">
         <f>vlookup($C16,Holidays!$A:$G,6)</f>
@@ -6050,22 +6126,22 @@
         <v>13.0</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q17" s="1">
         <v>1.0</v>
@@ -6127,22 +6203,22 @@
         <v>13.0</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q18" s="1">
         <v>2.0</v>
@@ -6204,28 +6280,28 @@
         <v>13.0</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q19" s="1">
         <v>2.0</v>
@@ -6286,22 +6362,22 @@
         <v>13.0</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q20" s="1">
         <v>4.0</v>
@@ -6367,34 +6443,34 @@
         <v>14.0</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q21" s="17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="S21" s="17" t="str">
         <f>vlookup($C21,Holidays!$A:$G,6)</f>
@@ -6453,34 +6529,34 @@
         <v>15.0</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q22" s="17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="S22" s="17" t="str">
         <f>vlookup($C22,Holidays!$A:$G,6)</f>
@@ -6539,34 +6615,34 @@
         <v>16.0</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q23" s="17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="S23" s="17" t="str">
         <f>vlookup($C23,Holidays!$A:$G,6)</f>
@@ -6628,34 +6704,34 @@
         <v>17.0</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q24" s="17" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="S24" s="17" t="str">
         <f>vlookup($C24,Holidays!$A:$G,6)</f>
@@ -6720,34 +6796,34 @@
         <v>18.0</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q25" s="17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="S25" s="17" t="str">
         <f>vlookup($C25,Holidays!$A:$G,6)</f>
@@ -6806,34 +6882,34 @@
         <v>19.0</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q26" s="17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="S26" s="17" t="str">
         <f>vlookup($C26,Holidays!$A:$G,6)</f>
@@ -6892,28 +6968,28 @@
         <v>20.0</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="Q27" s="17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="S27" s="17" t="str">
         <f>vlookup($C27,Holidays!$A:$G,6)</f>
@@ -6975,28 +7051,28 @@
         <v>21.0</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="Q28" s="17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R28" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="S28" s="17" t="str">
         <f>vlookup($C28,Holidays!$A:$G,6)</f>
@@ -7055,28 +7131,28 @@
         <v>22.0</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="Q29" s="17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="R29" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="S29" s="17" t="str">
         <f>vlookup($C29,Holidays!$A:$G,6)</f>
@@ -7138,28 +7214,28 @@
         <v>23.0</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="Q30" s="17" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="R30" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="S30" s="17" t="str">
         <f>vlookup($C30,Holidays!$A:$G,6)</f>
@@ -7218,28 +7294,28 @@
         <v>24.0</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="Q31" s="17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="S31" s="17" t="str">
         <f>vlookup($C31,Holidays!$A:$G,6)</f>
@@ -7298,28 +7374,28 @@
         <v>25.0</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="Q32" s="17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="R32" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="S32" s="17" t="str">
         <f>vlookup($C32,Holidays!$A:$G,6)</f>
@@ -7378,34 +7454,34 @@
         <v>26.0</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q33" s="17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="R33" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="S33" s="17" t="str">
         <f>vlookup($C33,Holidays!$A:$G,6)</f>
@@ -7467,34 +7543,34 @@
         <v>27.0</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q34" s="17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R34" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="S34" s="17" t="str">
         <f>vlookup($C34,Holidays!$A:$G,6)</f>
@@ -7553,34 +7629,34 @@
         <v>28.0</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q35" s="17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R35" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="S35" s="17" t="str">
         <f>vlookup($C35,Holidays!$A:$G,6)</f>
@@ -7639,34 +7715,34 @@
         <v>29.0</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q36" s="17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="R36" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="S36" s="17" t="str">
         <f>vlookup($C36,Holidays!$A:$G,6)</f>
@@ -7728,34 +7804,34 @@
         <v>30.0</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q37" s="17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R37" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="S37" s="17" t="str">
         <f>vlookup($C37,Holidays!$A:$G,6)</f>
@@ -7820,34 +7896,34 @@
         <v>31.0</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q38" s="17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="R38" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="S38" s="17" t="str">
         <f>vlookup($C38,Holidays!$A:$G,6)</f>
@@ -7906,28 +7982,28 @@
         <v>32.0</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="Q39" s="17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R39" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="S39" s="17" t="str">
         <f>vlookup($C39,Holidays!$A:$G,6)</f>
@@ -7986,28 +8062,28 @@
         <v>33.0</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="Q40" s="17" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="R40" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="S40" s="17" t="str">
         <f>vlookup($C40,Holidays!$A:$G,6)</f>
@@ -8069,28 +8145,28 @@
         <v>34.0</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="Q41" s="17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R41" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="S41" s="17" t="str">
         <f>vlookup($C41,Holidays!$A:$G,6)</f>
@@ -8152,28 +8228,28 @@
         <v>35.0</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="Q42" s="17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R42" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="S42" s="17" t="str">
         <f>vlookup($C42,Holidays!$A:$G,6)</f>
@@ -8232,28 +8308,28 @@
         <v>36.0</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="Q43" s="17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R43" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="S43" s="17" t="str">
         <f>vlookup($C43,Holidays!$A:$G,6)</f>
@@ -8318,28 +8394,28 @@
         <v>37.0</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="Q44" s="17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R44" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="S44" s="17" t="str">
         <f>vlookup($C44,Holidays!$A:$G,6)</f>
@@ -8404,34 +8480,34 @@
         <v>38.0</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q45" s="17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R45" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="S45" s="17" t="str">
         <f>vlookup($C45,Holidays!$A:$G,6)</f>
@@ -8496,34 +8572,34 @@
         <v>39.0</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q46" s="17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="R46" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="S46" s="17" t="str">
         <f>vlookup($C46,Holidays!$A:$G,6)</f>
@@ -8585,34 +8661,34 @@
         <v>40.0</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P47" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q47" s="17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R47" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="S47" s="17" t="str">
         <f>vlookup($C47,Holidays!$A:$G,6)</f>
@@ -8671,34 +8747,34 @@
         <v>41.0</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q48" s="17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="R48" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="S48" s="17" t="str">
         <f>vlookup($C48,Holidays!$A:$G,6)</f>
@@ -8763,34 +8839,34 @@
         <v>42.0</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M49" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P49" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q49" s="17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R49" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="S49" s="17" t="str">
         <f>vlookup($C49,Holidays!$A:$G,6)</f>
@@ -8852,34 +8928,34 @@
         <v>43.0</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q50" s="17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="R50" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="S50" s="17" t="str">
         <f>vlookup($C50,Holidays!$A:$G,6)</f>
@@ -8947,30 +9023,30 @@
         <v>44.0</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M51" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N51" s="1" t="str">
         <f t="shared" ref="N51:N56" si="50">if(J51="","",M51)</f>
         <v/>
       </c>
       <c r="O51" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P51" s="1" t="str">
         <f t="shared" ref="P51:P56" si="51">if(L51="","",O51)</f>
         <v/>
       </c>
       <c r="Q51" s="17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R51" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="S51" s="17" t="str">
         <f>vlookup($C51,Holidays!$A:$G,6)</f>
@@ -9032,30 +9108,30 @@
         <v>45.0</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N52" s="1" t="str">
         <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="O52" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P52" s="1" t="str">
         <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="Q52" s="17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="R52" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="S52" s="17" t="str">
         <f>vlookup($C52,Holidays!$A:$G,6)</f>
@@ -9120,30 +9196,30 @@
         <v>46.0</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N53" s="1" t="str">
         <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="O53" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P53" s="1" t="str">
         <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="Q53" s="17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R53" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="S53" s="17" t="str">
         <f>vlookup($C53,Holidays!$A:$G,6)</f>
@@ -9205,30 +9281,30 @@
         <v>47.0</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N54" s="1" t="str">
         <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="O54" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P54" s="1" t="str">
         <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="Q54" s="17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="R54" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="S54" s="17" t="str">
         <f>vlookup($C54,Holidays!$A:$G,6)</f>
@@ -9287,30 +9363,30 @@
         <v>48.0</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N55" s="1" t="str">
         <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="O55" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P55" s="1" t="str">
         <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="Q55" s="17" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="R55" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="S55" s="17" t="str">
         <f>vlookup($C55,Holidays!$A:$G,6)</f>
@@ -9369,30 +9445,30 @@
         <v>49.0</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N56" s="1" t="str">
         <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="O56" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P56" s="1" t="str">
         <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="Q56" s="17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R56" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="S56" s="17" t="str">
         <f>vlookup($C56,Holidays!$A:$G,6)</f>
@@ -12247,25 +12323,25 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="16" t="s">
+      <c r="A1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="1" t="s">
         <v>122</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -12274,1174 +12350,311 @@
       <c r="I1" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>126</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="B2" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="C2" s="5">
-        <f>vlookup($A2,Matchdays!$A:$G,3,false)</f>
-        <v>45794</v>
-      </c>
-      <c r="D2" s="1" t="str">
-        <f>vlookup($B2,Holidays!$A:$I,2)</f>
-        <v>Turkey</v>
-      </c>
-      <c r="E2" s="1" t="str">
-        <f>vlookup($B2,Holidays!$A:$I,3)</f>
-        <v>Belek</v>
-      </c>
-      <c r="F2" s="1" t="str">
-        <f>vlookup($A2,Matchdays!$A:$G,4,false)</f>
-        <v>Montgomerie</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="1">
         <v>1.0</v>
       </c>
-      <c r="I2" s="1">
-        <v>39.0</v>
-      </c>
-      <c r="J2" s="1">
-        <v>0.0</v>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="B3" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="C3" s="5">
-        <f>vlookup($A3,Matchdays!$A:$G,3,false)</f>
-        <v>45794</v>
-      </c>
-      <c r="D3" s="1" t="str">
-        <f>vlookup($B3,Holidays!$A:$I,2)</f>
-        <v>Turkey</v>
-      </c>
-      <c r="E3" s="1" t="str">
-        <f>vlookup($B3,Holidays!$A:$I,3)</f>
-        <v>Belek</v>
-      </c>
-      <c r="F3" s="1" t="str">
-        <f>vlookup($A3,Matchdays!$A:$G,4,false)</f>
-        <v>Montgomerie</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H3" s="1">
         <v>2.0</v>
       </c>
-      <c r="I3" s="1">
-        <v>34.0</v>
-      </c>
-      <c r="J3" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="K3" s="1">
+      <c r="B3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1">
         <v>1.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="B4" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="C4" s="5">
-        <f>vlookup($A4,Matchdays!$A:$G,3,false)</f>
-        <v>45794</v>
-      </c>
-      <c r="D4" s="1" t="str">
-        <f>vlookup($B4,Holidays!$A:$I,2)</f>
-        <v>Turkey</v>
-      </c>
-      <c r="E4" s="1" t="str">
-        <f>vlookup($B4,Holidays!$A:$I,3)</f>
-        <v>Belek</v>
-      </c>
-      <c r="F4" s="1" t="str">
-        <f>vlookup($A4,Matchdays!$A:$G,4,false)</f>
-        <v>Montgomerie</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="1">
         <v>3.0</v>
       </c>
-      <c r="I4" s="1">
-        <v>34.0</v>
-      </c>
-      <c r="J4" s="1">
-        <v>0.0</v>
+      <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="B5" s="1">
         <v>4.0</v>
       </c>
-      <c r="C5" s="5">
-        <f>vlookup($A5,Matchdays!$A:$G,3,false)</f>
-        <v>45794</v>
-      </c>
-      <c r="D5" s="1" t="str">
-        <f>vlookup($B5,Holidays!$A:$I,2)</f>
-        <v>Turkey</v>
-      </c>
-      <c r="E5" s="1" t="str">
-        <f>vlookup($B5,Holidays!$A:$I,3)</f>
-        <v>Belek</v>
-      </c>
-      <c r="F5" s="1" t="str">
-        <f>vlookup($A5,Matchdays!$A:$G,4,false)</f>
-        <v>Montgomerie</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="I5" s="1">
-        <v>34.0</v>
-      </c>
-      <c r="J5" s="1">
-        <v>0.0</v>
+      <c r="B5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="B6" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="C6" s="5">
-        <f>vlookup($A6,Matchdays!$A:$G,3,false)</f>
-        <v>45794</v>
-      </c>
-      <c r="D6" s="1" t="str">
-        <f>vlookup($B6,Holidays!$A:$I,2)</f>
-        <v>Turkey</v>
-      </c>
-      <c r="E6" s="1" t="str">
-        <f>vlookup($B6,Holidays!$A:$I,3)</f>
-        <v>Belek</v>
-      </c>
-      <c r="F6" s="1" t="str">
-        <f>vlookup($A6,Matchdays!$A:$G,4,false)</f>
-        <v>Montgomerie</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" s="1">
         <v>5.0</v>
       </c>
-      <c r="I6" s="1">
-        <v>32.0</v>
-      </c>
-      <c r="J6" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="K6" s="1">
-        <v>2.0</v>
+      <c r="B6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="B7" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="C7" s="5">
-        <f>vlookup($A7,Matchdays!$A:$G,3,false)</f>
-        <v>45794</v>
-      </c>
-      <c r="D7" s="1" t="str">
-        <f>vlookup($B7,Holidays!$A:$I,2)</f>
-        <v>Turkey</v>
-      </c>
-      <c r="E7" s="1" t="str">
-        <f>vlookup($B7,Holidays!$A:$I,3)</f>
-        <v>Belek</v>
-      </c>
-      <c r="F7" s="1" t="str">
-        <f>vlookup($A7,Matchdays!$A:$G,4,false)</f>
-        <v>Montgomerie</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" s="1">
         <v>6.0</v>
       </c>
-      <c r="I7" s="1">
-        <v>31.0</v>
-      </c>
-      <c r="J7" s="1">
-        <v>0.0</v>
+      <c r="B7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="B8" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="C8" s="5">
-        <f>vlookup($A8,Matchdays!$A:$G,3,false)</f>
-        <v>45794</v>
-      </c>
-      <c r="D8" s="1" t="str">
-        <f>vlookup($B8,Holidays!$A:$I,2)</f>
-        <v>Turkey</v>
-      </c>
-      <c r="E8" s="1" t="str">
-        <f>vlookup($B8,Holidays!$A:$I,3)</f>
-        <v>Belek</v>
-      </c>
-      <c r="F8" s="1" t="str">
-        <f>vlookup($A8,Matchdays!$A:$G,4,false)</f>
-        <v>Montgomerie</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H8" s="1">
         <v>7.0</v>
       </c>
-      <c r="I8" s="1">
-        <v>29.0</v>
-      </c>
-      <c r="J8" s="1">
-        <v>0.0</v>
+      <c r="B8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="B9" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="C9" s="5">
-        <f>vlookup($A9,Matchdays!$A:$G,3,false)</f>
-        <v>45794</v>
-      </c>
-      <c r="D9" s="1" t="str">
-        <f>vlookup($B9,Holidays!$A:$I,2)</f>
-        <v>Turkey</v>
-      </c>
-      <c r="E9" s="1" t="str">
-        <f>vlookup($B9,Holidays!$A:$I,3)</f>
-        <v>Belek</v>
-      </c>
-      <c r="F9" s="1" t="str">
-        <f>vlookup($A9,Matchdays!$A:$G,4,false)</f>
-        <v>Montgomerie</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9" s="1">
         <v>8.0</v>
       </c>
-      <c r="I9" s="1">
-        <v>28.0</v>
-      </c>
-      <c r="J9" s="1">
+      <c r="B9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="1">
         <v>0.0</v>
-      </c>
-      <c r="K9" s="1">
-        <v>1.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="B10" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="C10" s="5">
-        <f>vlookup($A10,Matchdays!$A:$G,3,false)</f>
-        <v>45794</v>
-      </c>
-      <c r="D10" s="1" t="str">
-        <f>vlookup($B10,Holidays!$A:$I,2)</f>
-        <v>Turkey</v>
-      </c>
-      <c r="E10" s="1" t="str">
-        <f>vlookup($B10,Holidays!$A:$I,3)</f>
-        <v>Belek</v>
-      </c>
-      <c r="F10" s="1" t="str">
-        <f>vlookup($A10,Matchdays!$A:$G,4,false)</f>
-        <v>Montgomerie</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10" s="1">
         <v>9.0</v>
       </c>
-      <c r="I10" s="1">
-        <v>28.0</v>
-      </c>
-      <c r="J10" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="K10" s="1">
-        <v>3.0</v>
+      <c r="B10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="B11" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="C11" s="5">
-        <f>vlookup($A11,Matchdays!$A:$G,3,false)</f>
-        <v>45794</v>
-      </c>
-      <c r="D11" s="1" t="str">
-        <f>vlookup($B11,Holidays!$A:$I,2)</f>
-        <v>Turkey</v>
-      </c>
-      <c r="E11" s="1" t="str">
-        <f>vlookup($B11,Holidays!$A:$I,3)</f>
-        <v>Belek</v>
-      </c>
-      <c r="F11" s="1" t="str">
-        <f>vlookup($A11,Matchdays!$A:$G,4,false)</f>
-        <v>Montgomerie</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H11" s="1">
         <v>10.0</v>
       </c>
-      <c r="I11" s="1">
-        <v>23.0</v>
-      </c>
-      <c r="J11" s="1">
+      <c r="B11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="1">
         <v>0.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="B12" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="C12" s="5">
-        <f>vlookup($A12,Matchdays!$A:$G,3,false)</f>
-        <v>45794</v>
-      </c>
-      <c r="D12" s="1" t="str">
-        <f>vlookup($B12,Holidays!$A:$I,2)</f>
-        <v>Turkey</v>
-      </c>
-      <c r="E12" s="1" t="str">
-        <f>vlookup($B12,Holidays!$A:$I,3)</f>
-        <v>Belek</v>
-      </c>
-      <c r="F12" s="1" t="str">
-        <f>vlookup($A12,Matchdays!$A:$G,4,false)</f>
-        <v>Montgomerie</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H12" s="1">
         <v>11.0</v>
       </c>
-      <c r="I12" s="1">
-        <v>23.0</v>
-      </c>
-      <c r="J12" s="1">
-        <v>0.0</v>
+      <c r="B12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="B13" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="C13" s="5">
-        <f>vlookup($A13,Matchdays!$A:$G,3,false)</f>
-        <v>45794</v>
-      </c>
-      <c r="D13" s="1" t="str">
-        <f>vlookup($B13,Holidays!$A:$I,2)</f>
-        <v>Turkey</v>
-      </c>
-      <c r="E13" s="1" t="str">
-        <f>vlookup($B13,Holidays!$A:$I,3)</f>
-        <v>Belek</v>
-      </c>
-      <c r="F13" s="1" t="str">
-        <f>vlookup($A13,Matchdays!$A:$G,4,false)</f>
-        <v>Montgomerie</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H13" s="27" t="s">
-        <v>127</v>
-      </c>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
+        <v>12.0</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="B14" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="C14" s="5">
-        <f>vlookup($A14,Matchdays!$A:$G,3,false)</f>
-        <v>45546</v>
-      </c>
-      <c r="D14" s="1" t="str">
-        <f>vlookup($B14,Holidays!$A:$I,2)</f>
-        <v>Spain</v>
-      </c>
-      <c r="E14" s="1" t="str">
-        <f>vlookup($B14,Holidays!$A:$I,3)</f>
-        <v>Malaga</v>
-      </c>
-      <c r="F14" s="1" t="str">
-        <f>vlookup($A14,Matchdays!$A:$G,4,false)</f>
-        <v>Miguel Angel Jimenez Academy</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H14" s="1">
-        <v>1.0</v>
+        <v>13.0</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="B15" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="C15" s="5">
-        <f>vlookup($A15,Matchdays!$A:$G,3,false)</f>
-        <v>45546</v>
-      </c>
-      <c r="D15" s="1" t="str">
-        <f>vlookup($B15,Holidays!$A:$I,2)</f>
-        <v>Spain</v>
-      </c>
-      <c r="E15" s="1" t="str">
-        <f>vlookup($B15,Holidays!$A:$I,3)</f>
-        <v>Malaga</v>
-      </c>
-      <c r="F15" s="1" t="str">
-        <f>vlookup($A15,Matchdays!$A:$G,4,false)</f>
-        <v>Miguel Angel Jimenez Academy</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H15" s="1">
-        <v>2.0</v>
+        <v>14.0</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="B16" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="C16" s="5">
-        <f>vlookup($A16,Matchdays!$A:$G,3,false)</f>
-        <v>45546</v>
-      </c>
-      <c r="D16" s="1" t="str">
-        <f>vlookup($B16,Holidays!$A:$I,2)</f>
-        <v>Spain</v>
-      </c>
-      <c r="E16" s="1" t="str">
-        <f>vlookup($B16,Holidays!$A:$I,3)</f>
-        <v>Malaga</v>
-      </c>
-      <c r="F16" s="1" t="str">
-        <f>vlookup($A16,Matchdays!$A:$G,4,false)</f>
-        <v>Miguel Angel Jimenez Academy</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H16" s="1">
-        <v>3.0</v>
+        <v>15.0</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="B17" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="C17" s="5">
-        <f>vlookup($A17,Matchdays!$A:$G,3,false)</f>
-        <v>45546</v>
-      </c>
-      <c r="D17" s="1" t="str">
-        <f>vlookup($B17,Holidays!$A:$I,2)</f>
-        <v>Spain</v>
-      </c>
-      <c r="E17" s="1" t="str">
-        <f>vlookup($B17,Holidays!$A:$I,3)</f>
-        <v>Malaga</v>
-      </c>
-      <c r="F17" s="1" t="str">
-        <f>vlookup($A17,Matchdays!$A:$G,4,false)</f>
-        <v>Miguel Angel Jimenez Academy</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H17" s="1">
-        <v>4.0</v>
+        <v>16.0</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E17" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="B18" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="C18" s="5">
-        <f>vlookup($A18,Matchdays!$A:$G,3,false)</f>
-        <v>45546</v>
-      </c>
-      <c r="D18" s="1" t="str">
-        <f>vlookup($B18,Holidays!$A:$I,2)</f>
-        <v>Spain</v>
-      </c>
-      <c r="E18" s="1" t="str">
-        <f>vlookup($B18,Holidays!$A:$I,3)</f>
-        <v>Malaga</v>
-      </c>
-      <c r="F18" s="1" t="str">
-        <f>vlookup($A18,Matchdays!$A:$G,4,false)</f>
-        <v>Miguel Angel Jimenez Academy</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H18" s="1">
-        <v>5.0</v>
+        <v>17.0</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E18" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="B19" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="C19" s="5">
-        <f>vlookup($A19,Matchdays!$A:$G,3,false)</f>
-        <v>45546</v>
-      </c>
-      <c r="D19" s="1" t="str">
-        <f>vlookup($B19,Holidays!$A:$I,2)</f>
-        <v>Spain</v>
-      </c>
-      <c r="E19" s="1" t="str">
-        <f>vlookup($B19,Holidays!$A:$I,3)</f>
-        <v>Malaga</v>
-      </c>
-      <c r="F19" s="1" t="str">
-        <f>vlookup($A19,Matchdays!$A:$G,4,false)</f>
-        <v>Miguel Angel Jimenez Academy</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H19" s="1">
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="B20" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="C20" s="5">
-        <f>vlookup($A20,Matchdays!$A:$G,3,false)</f>
-        <v>45546</v>
-      </c>
-      <c r="D20" s="1" t="str">
-        <f>vlookup($B20,Holidays!$A:$I,2)</f>
-        <v>Spain</v>
-      </c>
-      <c r="E20" s="1" t="str">
-        <f>vlookup($B20,Holidays!$A:$I,3)</f>
-        <v>Malaga</v>
-      </c>
-      <c r="F20" s="1" t="str">
-        <f>vlookup($A20,Matchdays!$A:$G,4,false)</f>
-        <v>Miguel Angel Jimenez Academy</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="H20" s="1">
-        <v>7.0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="B21" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="C21" s="5">
-        <f>vlookup($A21,Matchdays!$A:$G,3,false)</f>
-        <v>45546</v>
-      </c>
-      <c r="D21" s="1" t="str">
-        <f>vlookup($B21,Holidays!$A:$I,2)</f>
-        <v>Spain</v>
-      </c>
-      <c r="E21" s="1" t="str">
-        <f>vlookup($B21,Holidays!$A:$I,3)</f>
-        <v>Malaga</v>
-      </c>
-      <c r="F21" s="1" t="str">
-        <f>vlookup($A21,Matchdays!$A:$G,4,false)</f>
-        <v>Miguel Angel Jimenez Academy</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H21" s="1">
-        <v>8.0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="B22" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="C22" s="5">
-        <f>vlookup($A22,Matchdays!$A:$G,3,false)</f>
-        <v>45546</v>
-      </c>
-      <c r="D22" s="1" t="str">
-        <f>vlookup($B22,Holidays!$A:$I,2)</f>
-        <v>Spain</v>
-      </c>
-      <c r="E22" s="1" t="str">
-        <f>vlookup($B22,Holidays!$A:$I,3)</f>
-        <v>Malaga</v>
-      </c>
-      <c r="F22" s="1" t="str">
-        <f>vlookup($A22,Matchdays!$A:$G,4,false)</f>
-        <v>Miguel Angel Jimenez Academy</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H22" s="1">
-        <v>9.0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="B23" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="C23" s="5">
-        <f>vlookup($A23,Matchdays!$A:$G,3,false)</f>
-        <v>45546</v>
-      </c>
-      <c r="D23" s="1" t="str">
-        <f>vlookup($B23,Holidays!$A:$I,2)</f>
-        <v>Spain</v>
-      </c>
-      <c r="E23" s="1" t="str">
-        <f>vlookup($B23,Holidays!$A:$I,3)</f>
-        <v>Malaga</v>
-      </c>
-      <c r="F23" s="1" t="str">
-        <f>vlookup($A23,Matchdays!$A:$G,4,false)</f>
-        <v>Miguel Angel Jimenez Academy</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H23" s="1">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="B24" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="C24" s="5">
-        <f>vlookup($A24,Matchdays!$A:$G,3,false)</f>
-        <v>45546</v>
-      </c>
-      <c r="D24" s="1" t="str">
-        <f>vlookup($B24,Holidays!$A:$I,2)</f>
-        <v>Spain</v>
-      </c>
-      <c r="E24" s="1" t="str">
-        <f>vlookup($B24,Holidays!$A:$I,3)</f>
-        <v>Malaga</v>
-      </c>
-      <c r="F24" s="1" t="str">
-        <f>vlookup($A24,Matchdays!$A:$G,4,false)</f>
-        <v>Miguel Angel Jimenez Academy</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H24" s="1">
-        <v>11.0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="B25" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="C25" s="5">
-        <f>vlookup($A25,Matchdays!$A:$G,3,false)</f>
-        <v>45546</v>
-      </c>
-      <c r="D25" s="1" t="str">
-        <f>vlookup($B25,Holidays!$A:$I,2)</f>
-        <v>Spain</v>
-      </c>
-      <c r="E25" s="1" t="str">
-        <f>vlookup($B25,Holidays!$A:$I,3)</f>
-        <v>Malaga</v>
-      </c>
-      <c r="F25" s="1" t="str">
-        <f>vlookup($A25,Matchdays!$A:$G,4,false)</f>
-        <v>Miguel Angel Jimenez Academy</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H25" s="1">
-        <v>12.0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="B26" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="C26" s="5">
-        <f>vlookup($A26,Matchdays!$A:$G,3,false)</f>
-        <v>45074</v>
-      </c>
-      <c r="D26" s="1" t="str">
-        <f>vlookup($B26,Holidays!$A:$I,2)</f>
-        <v>Spain</v>
-      </c>
-      <c r="E26" s="1" t="str">
-        <f>vlookup($B26,Holidays!$A:$I,3)</f>
-        <v>Murcia</v>
-      </c>
-      <c r="F26" s="1" t="str">
-        <f>vlookup($A26,Matchdays!$A:$G,4,false)</f>
-        <v>Saurines</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H26" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E19" s="1">
         <v>1.0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="B27" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="C27" s="5">
-        <f>vlookup($A27,Matchdays!$A:$G,3,false)</f>
-        <v>45074</v>
-      </c>
-      <c r="D27" s="1" t="str">
-        <f>vlookup($B27,Holidays!$A:$I,2)</f>
-        <v>Spain</v>
-      </c>
-      <c r="E27" s="1" t="str">
-        <f>vlookup($B27,Holidays!$A:$I,3)</f>
-        <v>Murcia</v>
-      </c>
-      <c r="F27" s="1" t="str">
-        <f>vlookup($A27,Matchdays!$A:$G,4,false)</f>
-        <v>Saurines</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="B28" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="C28" s="5">
-        <f>vlookup($A28,Matchdays!$A:$G,3,false)</f>
-        <v>45074</v>
-      </c>
-      <c r="D28" s="1" t="str">
-        <f>vlookup($B28,Holidays!$A:$I,2)</f>
-        <v>Spain</v>
-      </c>
-      <c r="E28" s="1" t="str">
-        <f>vlookup($B28,Holidays!$A:$I,3)</f>
-        <v>Murcia</v>
-      </c>
-      <c r="F28" s="1" t="str">
-        <f>vlookup($A28,Matchdays!$A:$G,4,false)</f>
-        <v>Saurines</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="K28" s="1">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="B29" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="C29" s="5">
-        <f>vlookup($A29,Matchdays!$A:$G,3,false)</f>
-        <v>45074</v>
-      </c>
-      <c r="D29" s="1" t="str">
-        <f>vlookup($B29,Holidays!$A:$I,2)</f>
-        <v>Spain</v>
-      </c>
-      <c r="E29" s="1" t="str">
-        <f>vlookup($B29,Holidays!$A:$I,3)</f>
-        <v>Murcia</v>
-      </c>
-      <c r="F29" s="1" t="str">
-        <f>vlookup($A29,Matchdays!$A:$G,4,false)</f>
-        <v>Saurines</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="B30" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="C30" s="5">
-        <f>vlookup($A30,Matchdays!$A:$G,3,false)</f>
-        <v>45074</v>
-      </c>
-      <c r="D30" s="1" t="str">
-        <f>vlookup($B30,Holidays!$A:$I,2)</f>
-        <v>Spain</v>
-      </c>
-      <c r="E30" s="1" t="str">
-        <f>vlookup($B30,Holidays!$A:$I,3)</f>
-        <v>Murcia</v>
-      </c>
-      <c r="F30" s="1" t="str">
-        <f>vlookup($A30,Matchdays!$A:$G,4,false)</f>
-        <v>Saurines</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="B31" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="C31" s="5">
-        <f>vlookup($A31,Matchdays!$A:$G,3,false)</f>
-        <v>45074</v>
-      </c>
-      <c r="D31" s="1" t="str">
-        <f>vlookup($B31,Holidays!$A:$I,2)</f>
-        <v>Spain</v>
-      </c>
-      <c r="E31" s="1" t="str">
-        <f>vlookup($B31,Holidays!$A:$I,3)</f>
-        <v>Murcia</v>
-      </c>
-      <c r="F31" s="1" t="str">
-        <f>vlookup($A31,Matchdays!$A:$G,4,false)</f>
-        <v>Saurines</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="B32" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="C32" s="5">
-        <f>vlookup($A32,Matchdays!$A:$G,3,false)</f>
-        <v>45074</v>
-      </c>
-      <c r="D32" s="1" t="str">
-        <f>vlookup($B32,Holidays!$A:$I,2)</f>
-        <v>Spain</v>
-      </c>
-      <c r="E32" s="1" t="str">
-        <f>vlookup($B32,Holidays!$A:$I,3)</f>
-        <v>Murcia</v>
-      </c>
-      <c r="F32" s="1" t="str">
-        <f>vlookup($A32,Matchdays!$A:$G,4,false)</f>
-        <v>Saurines</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="B33" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="C33" s="5">
-        <f>vlookup($A33,Matchdays!$A:$G,3,false)</f>
-        <v>45074</v>
-      </c>
-      <c r="D33" s="1" t="str">
-        <f>vlookup($B33,Holidays!$A:$I,2)</f>
-        <v>Spain</v>
-      </c>
-      <c r="E33" s="1" t="str">
-        <f>vlookup($B33,Holidays!$A:$I,3)</f>
-        <v>Murcia</v>
-      </c>
-      <c r="F33" s="1" t="str">
-        <f>vlookup($A33,Matchdays!$A:$G,4,false)</f>
-        <v>Saurines</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H33" s="6" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="B34" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="C34" s="5">
-        <f>vlookup($A34,Matchdays!$A:$G,3,false)</f>
-        <v>45074</v>
-      </c>
-      <c r="D34" s="1" t="str">
-        <f>vlookup($B34,Holidays!$A:$I,2)</f>
-        <v>Spain</v>
-      </c>
-      <c r="E34" s="1" t="str">
-        <f>vlookup($B34,Holidays!$A:$I,3)</f>
-        <v>Murcia</v>
-      </c>
-      <c r="F34" s="1" t="str">
-        <f>vlookup($A34,Matchdays!$A:$G,4,false)</f>
-        <v>Saurines</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="B35" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="C35" s="5">
-        <f>vlookup($A35,Matchdays!$A:$G,3,false)</f>
-        <v>45074</v>
-      </c>
-      <c r="D35" s="1" t="str">
-        <f>vlookup($B35,Holidays!$A:$I,2)</f>
-        <v>Spain</v>
-      </c>
-      <c r="E35" s="1" t="str">
-        <f>vlookup($B35,Holidays!$A:$I,3)</f>
-        <v>Murcia</v>
-      </c>
-      <c r="F35" s="1" t="str">
-        <f>vlookup($A35,Matchdays!$A:$G,4,false)</f>
-        <v>Saurines</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="B36" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="C36" s="5">
-        <f>vlookup($A36,Matchdays!$A:$G,3,false)</f>
-        <v>45074</v>
-      </c>
-      <c r="D36" s="1" t="str">
-        <f>vlookup($B36,Holidays!$A:$I,2)</f>
-        <v>Spain</v>
-      </c>
-      <c r="E36" s="1" t="str">
-        <f>vlookup($B36,Holidays!$A:$I,3)</f>
-        <v>Murcia</v>
-      </c>
-      <c r="F36" s="1" t="str">
-        <f>vlookup($A36,Matchdays!$A:$G,4,false)</f>
-        <v>Saurines</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="B37" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="C37" s="5">
-        <f>vlookup($A37,Matchdays!$A:$G,3,false)</f>
-        <v>45074</v>
-      </c>
-      <c r="D37" s="1" t="str">
-        <f>vlookup($B37,Holidays!$A:$I,2)</f>
-        <v>Spain</v>
-      </c>
-      <c r="E37" s="1" t="str">
-        <f>vlookup($B37,Holidays!$A:$I,3)</f>
-        <v>Murcia</v>
-      </c>
-      <c r="F37" s="1" t="str">
-        <f>vlookup($A37,Matchdays!$A:$G,4,false)</f>
-        <v>Saurines</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H37" s="6" t="s">
-        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -13457,53 +12670,1263 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="B2" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C2" s="5">
+        <f>vlookup($A2,Matchdays!$A:$G,3,false)</f>
+        <v>45794</v>
+      </c>
+      <c r="D2" s="1" t="str">
+        <f>vlookup($B2,Holidays!$A:$I,2)</f>
+        <v>Turkey</v>
+      </c>
+      <c r="E2" s="1" t="str">
+        <f>vlookup($B2,Holidays!$A:$I,3)</f>
+        <v>Belek</v>
+      </c>
+      <c r="F2" s="1" t="str">
+        <f>vlookup($A2,Matchdays!$A:$G,4,false)</f>
+        <v>Montgomerie</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I2" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="B3" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C3" s="5">
+        <f>vlookup($A3,Matchdays!$A:$G,3,false)</f>
+        <v>45794</v>
+      </c>
+      <c r="D3" s="1" t="str">
+        <f>vlookup($B3,Holidays!$A:$I,2)</f>
+        <v>Turkey</v>
+      </c>
+      <c r="E3" s="1" t="str">
+        <f>vlookup($B3,Holidays!$A:$I,3)</f>
+        <v>Belek</v>
+      </c>
+      <c r="F3" s="1" t="str">
+        <f>vlookup($A3,Matchdays!$A:$G,4,false)</f>
+        <v>Montgomerie</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H3" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="I3" s="1">
+        <v>34.0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="B4" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C4" s="5">
+        <f>vlookup($A4,Matchdays!$A:$G,3,false)</f>
+        <v>45794</v>
+      </c>
+      <c r="D4" s="1" t="str">
+        <f>vlookup($B4,Holidays!$A:$I,2)</f>
+        <v>Turkey</v>
+      </c>
+      <c r="E4" s="1" t="str">
+        <f>vlookup($B4,Holidays!$A:$I,3)</f>
+        <v>Belek</v>
+      </c>
+      <c r="F4" s="1" t="str">
+        <f>vlookup($A4,Matchdays!$A:$G,4,false)</f>
+        <v>Montgomerie</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="I4" s="1">
+        <v>34.0</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="B5" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C5" s="5">
+        <f>vlookup($A5,Matchdays!$A:$G,3,false)</f>
+        <v>45794</v>
+      </c>
+      <c r="D5" s="1" t="str">
+        <f>vlookup($B5,Holidays!$A:$I,2)</f>
+        <v>Turkey</v>
+      </c>
+      <c r="E5" s="1" t="str">
+        <f>vlookup($B5,Holidays!$A:$I,3)</f>
+        <v>Belek</v>
+      </c>
+      <c r="F5" s="1" t="str">
+        <f>vlookup($A5,Matchdays!$A:$G,4,false)</f>
+        <v>Montgomerie</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="I5" s="1">
+        <v>34.0</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="B6" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C6" s="5">
+        <f>vlookup($A6,Matchdays!$A:$G,3,false)</f>
+        <v>45794</v>
+      </c>
+      <c r="D6" s="1" t="str">
+        <f>vlookup($B6,Holidays!$A:$I,2)</f>
+        <v>Turkey</v>
+      </c>
+      <c r="E6" s="1" t="str">
+        <f>vlookup($B6,Holidays!$A:$I,3)</f>
+        <v>Belek</v>
+      </c>
+      <c r="F6" s="1" t="str">
+        <f>vlookup($A6,Matchdays!$A:$G,4,false)</f>
+        <v>Montgomerie</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>32.0</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="B7" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C7" s="5">
+        <f>vlookup($A7,Matchdays!$A:$G,3,false)</f>
+        <v>45794</v>
+      </c>
+      <c r="D7" s="1" t="str">
+        <f>vlookup($B7,Holidays!$A:$I,2)</f>
+        <v>Turkey</v>
+      </c>
+      <c r="E7" s="1" t="str">
+        <f>vlookup($B7,Holidays!$A:$I,3)</f>
+        <v>Belek</v>
+      </c>
+      <c r="F7" s="1" t="str">
+        <f>vlookup($A7,Matchdays!$A:$G,4,false)</f>
+        <v>Montgomerie</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="B8" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C8" s="5">
+        <f>vlookup($A8,Matchdays!$A:$G,3,false)</f>
+        <v>45794</v>
+      </c>
+      <c r="D8" s="1" t="str">
+        <f>vlookup($B8,Holidays!$A:$I,2)</f>
+        <v>Turkey</v>
+      </c>
+      <c r="E8" s="1" t="str">
+        <f>vlookup($B8,Holidays!$A:$I,3)</f>
+        <v>Belek</v>
+      </c>
+      <c r="F8" s="1" t="str">
+        <f>vlookup($A8,Matchdays!$A:$G,4,false)</f>
+        <v>Montgomerie</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="I8" s="1">
+        <v>29.0</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="B9" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C9" s="5">
+        <f>vlookup($A9,Matchdays!$A:$G,3,false)</f>
+        <v>45794</v>
+      </c>
+      <c r="D9" s="1" t="str">
+        <f>vlookup($B9,Holidays!$A:$I,2)</f>
+        <v>Turkey</v>
+      </c>
+      <c r="E9" s="1" t="str">
+        <f>vlookup($B9,Holidays!$A:$I,3)</f>
+        <v>Belek</v>
+      </c>
+      <c r="F9" s="1" t="str">
+        <f>vlookup($A9,Matchdays!$A:$G,4,false)</f>
+        <v>Montgomerie</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="I9" s="1">
+        <v>28.0</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="K9" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="B10" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C10" s="5">
+        <f>vlookup($A10,Matchdays!$A:$G,3,false)</f>
+        <v>45794</v>
+      </c>
+      <c r="D10" s="1" t="str">
+        <f>vlookup($B10,Holidays!$A:$I,2)</f>
+        <v>Turkey</v>
+      </c>
+      <c r="E10" s="1" t="str">
+        <f>vlookup($B10,Holidays!$A:$I,3)</f>
+        <v>Belek</v>
+      </c>
+      <c r="F10" s="1" t="str">
+        <f>vlookup($A10,Matchdays!$A:$G,4,false)</f>
+        <v>Montgomerie</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="I10" s="1">
+        <v>28.0</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="K10" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="B11" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C11" s="5">
+        <f>vlookup($A11,Matchdays!$A:$G,3,false)</f>
+        <v>45794</v>
+      </c>
+      <c r="D11" s="1" t="str">
+        <f>vlookup($B11,Holidays!$A:$I,2)</f>
+        <v>Turkey</v>
+      </c>
+      <c r="E11" s="1" t="str">
+        <f>vlookup($B11,Holidays!$A:$I,3)</f>
+        <v>Belek</v>
+      </c>
+      <c r="F11" s="1" t="str">
+        <f>vlookup($A11,Matchdays!$A:$G,4,false)</f>
+        <v>Montgomerie</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="I11" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="B12" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C12" s="5">
+        <f>vlookup($A12,Matchdays!$A:$G,3,false)</f>
+        <v>45794</v>
+      </c>
+      <c r="D12" s="1" t="str">
+        <f>vlookup($B12,Holidays!$A:$I,2)</f>
+        <v>Turkey</v>
+      </c>
+      <c r="E12" s="1" t="str">
+        <f>vlookup($B12,Holidays!$A:$I,3)</f>
+        <v>Belek</v>
+      </c>
+      <c r="F12" s="1" t="str">
+        <f>vlookup($A12,Matchdays!$A:$G,4,false)</f>
+        <v>Montgomerie</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H12" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="B13" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C13" s="5">
+        <f>vlookup($A13,Matchdays!$A:$G,3,false)</f>
+        <v>45794</v>
+      </c>
+      <c r="D13" s="1" t="str">
+        <f>vlookup($B13,Holidays!$A:$I,2)</f>
+        <v>Turkey</v>
+      </c>
+      <c r="E13" s="1" t="str">
+        <f>vlookup($B13,Holidays!$A:$I,3)</f>
+        <v>Belek</v>
+      </c>
+      <c r="F13" s="1" t="str">
+        <f>vlookup($A13,Matchdays!$A:$G,4,false)</f>
+        <v>Montgomerie</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="B14" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C14" s="5">
+        <f>vlookup($A14,Matchdays!$A:$G,3,false)</f>
+        <v>45546</v>
+      </c>
+      <c r="D14" s="1" t="str">
+        <f>vlookup($B14,Holidays!$A:$I,2)</f>
+        <v>Spain</v>
+      </c>
+      <c r="E14" s="1" t="str">
+        <f>vlookup($B14,Holidays!$A:$I,3)</f>
+        <v>Malaga</v>
+      </c>
+      <c r="F14" s="1" t="str">
+        <f>vlookup($A14,Matchdays!$A:$G,4,false)</f>
+        <v>Miguel Angel Jimenez Academy</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="B15" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C15" s="5">
+        <f>vlookup($A15,Matchdays!$A:$G,3,false)</f>
+        <v>45546</v>
+      </c>
+      <c r="D15" s="1" t="str">
+        <f>vlookup($B15,Holidays!$A:$I,2)</f>
+        <v>Spain</v>
+      </c>
+      <c r="E15" s="1" t="str">
+        <f>vlookup($B15,Holidays!$A:$I,3)</f>
+        <v>Malaga</v>
+      </c>
+      <c r="F15" s="1" t="str">
+        <f>vlookup($A15,Matchdays!$A:$G,4,false)</f>
+        <v>Miguel Angel Jimenez Academy</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="B16" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C16" s="5">
+        <f>vlookup($A16,Matchdays!$A:$G,3,false)</f>
+        <v>45546</v>
+      </c>
+      <c r="D16" s="1" t="str">
+        <f>vlookup($B16,Holidays!$A:$I,2)</f>
+        <v>Spain</v>
+      </c>
+      <c r="E16" s="1" t="str">
+        <f>vlookup($B16,Holidays!$A:$I,3)</f>
+        <v>Malaga</v>
+      </c>
+      <c r="F16" s="1" t="str">
+        <f>vlookup($A16,Matchdays!$A:$G,4,false)</f>
+        <v>Miguel Angel Jimenez Academy</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H16" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="B17" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C17" s="5">
+        <f>vlookup($A17,Matchdays!$A:$G,3,false)</f>
+        <v>45546</v>
+      </c>
+      <c r="D17" s="1" t="str">
+        <f>vlookup($B17,Holidays!$A:$I,2)</f>
+        <v>Spain</v>
+      </c>
+      <c r="E17" s="1" t="str">
+        <f>vlookup($B17,Holidays!$A:$I,3)</f>
+        <v>Malaga</v>
+      </c>
+      <c r="F17" s="1" t="str">
+        <f>vlookup($A17,Matchdays!$A:$G,4,false)</f>
+        <v>Miguel Angel Jimenez Academy</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H17" s="1">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="B18" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C18" s="5">
+        <f>vlookup($A18,Matchdays!$A:$G,3,false)</f>
+        <v>45546</v>
+      </c>
+      <c r="D18" s="1" t="str">
+        <f>vlookup($B18,Holidays!$A:$I,2)</f>
+        <v>Spain</v>
+      </c>
+      <c r="E18" s="1" t="str">
+        <f>vlookup($B18,Holidays!$A:$I,3)</f>
+        <v>Malaga</v>
+      </c>
+      <c r="F18" s="1" t="str">
+        <f>vlookup($A18,Matchdays!$A:$G,4,false)</f>
+        <v>Miguel Angel Jimenez Academy</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H18" s="1">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="B19" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C19" s="5">
+        <f>vlookup($A19,Matchdays!$A:$G,3,false)</f>
+        <v>45546</v>
+      </c>
+      <c r="D19" s="1" t="str">
+        <f>vlookup($B19,Holidays!$A:$I,2)</f>
+        <v>Spain</v>
+      </c>
+      <c r="E19" s="1" t="str">
+        <f>vlookup($B19,Holidays!$A:$I,3)</f>
+        <v>Malaga</v>
+      </c>
+      <c r="F19" s="1" t="str">
+        <f>vlookup($A19,Matchdays!$A:$G,4,false)</f>
+        <v>Miguel Angel Jimenez Academy</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H19" s="1">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="B20" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C20" s="5">
+        <f>vlookup($A20,Matchdays!$A:$G,3,false)</f>
+        <v>45546</v>
+      </c>
+      <c r="D20" s="1" t="str">
+        <f>vlookup($B20,Holidays!$A:$I,2)</f>
+        <v>Spain</v>
+      </c>
+      <c r="E20" s="1" t="str">
+        <f>vlookup($B20,Holidays!$A:$I,3)</f>
+        <v>Malaga</v>
+      </c>
+      <c r="F20" s="1" t="str">
+        <f>vlookup($A20,Matchdays!$A:$G,4,false)</f>
+        <v>Miguel Angel Jimenez Academy</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H20" s="1">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="B21" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C21" s="5">
+        <f>vlookup($A21,Matchdays!$A:$G,3,false)</f>
+        <v>45546</v>
+      </c>
+      <c r="D21" s="1" t="str">
+        <f>vlookup($B21,Holidays!$A:$I,2)</f>
+        <v>Spain</v>
+      </c>
+      <c r="E21" s="1" t="str">
+        <f>vlookup($B21,Holidays!$A:$I,3)</f>
+        <v>Malaga</v>
+      </c>
+      <c r="F21" s="1" t="str">
+        <f>vlookup($A21,Matchdays!$A:$G,4,false)</f>
+        <v>Miguel Angel Jimenez Academy</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="1">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="B22" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C22" s="5">
+        <f>vlookup($A22,Matchdays!$A:$G,3,false)</f>
+        <v>45546</v>
+      </c>
+      <c r="D22" s="1" t="str">
+        <f>vlookup($B22,Holidays!$A:$I,2)</f>
+        <v>Spain</v>
+      </c>
+      <c r="E22" s="1" t="str">
+        <f>vlookup($B22,Holidays!$A:$I,3)</f>
+        <v>Malaga</v>
+      </c>
+      <c r="F22" s="1" t="str">
+        <f>vlookup($A22,Matchdays!$A:$G,4,false)</f>
+        <v>Miguel Angel Jimenez Academy</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" s="1">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="B23" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C23" s="5">
+        <f>vlookup($A23,Matchdays!$A:$G,3,false)</f>
+        <v>45546</v>
+      </c>
+      <c r="D23" s="1" t="str">
+        <f>vlookup($B23,Holidays!$A:$I,2)</f>
+        <v>Spain</v>
+      </c>
+      <c r="E23" s="1" t="str">
+        <f>vlookup($B23,Holidays!$A:$I,3)</f>
+        <v>Malaga</v>
+      </c>
+      <c r="F23" s="1" t="str">
+        <f>vlookup($A23,Matchdays!$A:$G,4,false)</f>
+        <v>Miguel Angel Jimenez Academy</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" s="1">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="B24" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C24" s="5">
+        <f>vlookup($A24,Matchdays!$A:$G,3,false)</f>
+        <v>45546</v>
+      </c>
+      <c r="D24" s="1" t="str">
+        <f>vlookup($B24,Holidays!$A:$I,2)</f>
+        <v>Spain</v>
+      </c>
+      <c r="E24" s="1" t="str">
+        <f>vlookup($B24,Holidays!$A:$I,3)</f>
+        <v>Malaga</v>
+      </c>
+      <c r="F24" s="1" t="str">
+        <f>vlookup($A24,Matchdays!$A:$G,4,false)</f>
+        <v>Miguel Angel Jimenez Academy</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" s="1">
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="B25" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C25" s="5">
+        <f>vlookup($A25,Matchdays!$A:$G,3,false)</f>
+        <v>45546</v>
+      </c>
+      <c r="D25" s="1" t="str">
+        <f>vlookup($B25,Holidays!$A:$I,2)</f>
+        <v>Spain</v>
+      </c>
+      <c r="E25" s="1" t="str">
+        <f>vlookup($B25,Holidays!$A:$I,3)</f>
+        <v>Malaga</v>
+      </c>
+      <c r="F25" s="1" t="str">
+        <f>vlookup($A25,Matchdays!$A:$G,4,false)</f>
+        <v>Miguel Angel Jimenez Academy</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" s="1">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="B26" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C26" s="5">
+        <f>vlookup($A26,Matchdays!$A:$G,3,false)</f>
+        <v>45074</v>
+      </c>
+      <c r="D26" s="1" t="str">
+        <f>vlookup($B26,Holidays!$A:$I,2)</f>
+        <v>Spain</v>
+      </c>
+      <c r="E26" s="1" t="str">
+        <f>vlookup($B26,Holidays!$A:$I,3)</f>
+        <v>Murcia</v>
+      </c>
+      <c r="F26" s="1" t="str">
+        <f>vlookup($A26,Matchdays!$A:$G,4,false)</f>
+        <v>Saurines</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H26" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="B27" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C27" s="5">
+        <f>vlookup($A27,Matchdays!$A:$G,3,false)</f>
+        <v>45074</v>
+      </c>
+      <c r="D27" s="1" t="str">
+        <f>vlookup($B27,Holidays!$A:$I,2)</f>
+        <v>Spain</v>
+      </c>
+      <c r="E27" s="1" t="str">
+        <f>vlookup($B27,Holidays!$A:$I,3)</f>
+        <v>Murcia</v>
+      </c>
+      <c r="F27" s="1" t="str">
+        <f>vlookup($A27,Matchdays!$A:$G,4,false)</f>
+        <v>Saurines</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="B28" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C28" s="5">
+        <f>vlookup($A28,Matchdays!$A:$G,3,false)</f>
+        <v>45074</v>
+      </c>
+      <c r="D28" s="1" t="str">
+        <f>vlookup($B28,Holidays!$A:$I,2)</f>
+        <v>Spain</v>
+      </c>
+      <c r="E28" s="1" t="str">
+        <f>vlookup($B28,Holidays!$A:$I,3)</f>
+        <v>Murcia</v>
+      </c>
+      <c r="F28" s="1" t="str">
+        <f>vlookup($A28,Matchdays!$A:$G,4,false)</f>
+        <v>Saurines</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="K28" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="B29" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C29" s="5">
+        <f>vlookup($A29,Matchdays!$A:$G,3,false)</f>
+        <v>45074</v>
+      </c>
+      <c r="D29" s="1" t="str">
+        <f>vlookup($B29,Holidays!$A:$I,2)</f>
+        <v>Spain</v>
+      </c>
+      <c r="E29" s="1" t="str">
+        <f>vlookup($B29,Holidays!$A:$I,3)</f>
+        <v>Murcia</v>
+      </c>
+      <c r="F29" s="1" t="str">
+        <f>vlookup($A29,Matchdays!$A:$G,4,false)</f>
+        <v>Saurines</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="B30" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C30" s="5">
+        <f>vlookup($A30,Matchdays!$A:$G,3,false)</f>
+        <v>45074</v>
+      </c>
+      <c r="D30" s="1" t="str">
+        <f>vlookup($B30,Holidays!$A:$I,2)</f>
+        <v>Spain</v>
+      </c>
+      <c r="E30" s="1" t="str">
+        <f>vlookup($B30,Holidays!$A:$I,3)</f>
+        <v>Murcia</v>
+      </c>
+      <c r="F30" s="1" t="str">
+        <f>vlookup($A30,Matchdays!$A:$G,4,false)</f>
+        <v>Saurines</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="B31" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C31" s="5">
+        <f>vlookup($A31,Matchdays!$A:$G,3,false)</f>
+        <v>45074</v>
+      </c>
+      <c r="D31" s="1" t="str">
+        <f>vlookup($B31,Holidays!$A:$I,2)</f>
+        <v>Spain</v>
+      </c>
+      <c r="E31" s="1" t="str">
+        <f>vlookup($B31,Holidays!$A:$I,3)</f>
+        <v>Murcia</v>
+      </c>
+      <c r="F31" s="1" t="str">
+        <f>vlookup($A31,Matchdays!$A:$G,4,false)</f>
+        <v>Saurines</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="B32" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C32" s="5">
+        <f>vlookup($A32,Matchdays!$A:$G,3,false)</f>
+        <v>45074</v>
+      </c>
+      <c r="D32" s="1" t="str">
+        <f>vlookup($B32,Holidays!$A:$I,2)</f>
+        <v>Spain</v>
+      </c>
+      <c r="E32" s="1" t="str">
+        <f>vlookup($B32,Holidays!$A:$I,3)</f>
+        <v>Murcia</v>
+      </c>
+      <c r="F32" s="1" t="str">
+        <f>vlookup($A32,Matchdays!$A:$G,4,false)</f>
+        <v>Saurines</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="B33" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C33" s="5">
+        <f>vlookup($A33,Matchdays!$A:$G,3,false)</f>
+        <v>45074</v>
+      </c>
+      <c r="D33" s="1" t="str">
+        <f>vlookup($B33,Holidays!$A:$I,2)</f>
+        <v>Spain</v>
+      </c>
+      <c r="E33" s="1" t="str">
+        <f>vlookup($B33,Holidays!$A:$I,3)</f>
+        <v>Murcia</v>
+      </c>
+      <c r="F33" s="1" t="str">
+        <f>vlookup($A33,Matchdays!$A:$G,4,false)</f>
+        <v>Saurines</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="B34" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C34" s="5">
+        <f>vlookup($A34,Matchdays!$A:$G,3,false)</f>
+        <v>45074</v>
+      </c>
+      <c r="D34" s="1" t="str">
+        <f>vlookup($B34,Holidays!$A:$I,2)</f>
+        <v>Spain</v>
+      </c>
+      <c r="E34" s="1" t="str">
+        <f>vlookup($B34,Holidays!$A:$I,3)</f>
+        <v>Murcia</v>
+      </c>
+      <c r="F34" s="1" t="str">
+        <f>vlookup($A34,Matchdays!$A:$G,4,false)</f>
+        <v>Saurines</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="B35" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C35" s="5">
+        <f>vlookup($A35,Matchdays!$A:$G,3,false)</f>
+        <v>45074</v>
+      </c>
+      <c r="D35" s="1" t="str">
+        <f>vlookup($B35,Holidays!$A:$I,2)</f>
+        <v>Spain</v>
+      </c>
+      <c r="E35" s="1" t="str">
+        <f>vlookup($B35,Holidays!$A:$I,3)</f>
+        <v>Murcia</v>
+      </c>
+      <c r="F35" s="1" t="str">
+        <f>vlookup($A35,Matchdays!$A:$G,4,false)</f>
+        <v>Saurines</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="B36" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C36" s="5">
+        <f>vlookup($A36,Matchdays!$A:$G,3,false)</f>
+        <v>45074</v>
+      </c>
+      <c r="D36" s="1" t="str">
+        <f>vlookup($B36,Holidays!$A:$I,2)</f>
+        <v>Spain</v>
+      </c>
+      <c r="E36" s="1" t="str">
+        <f>vlookup($B36,Holidays!$A:$I,3)</f>
+        <v>Murcia</v>
+      </c>
+      <c r="F36" s="1" t="str">
+        <f>vlookup($A36,Matchdays!$A:$G,4,false)</f>
+        <v>Saurines</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="B37" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C37" s="5">
+        <f>vlookup($A37,Matchdays!$A:$G,3,false)</f>
+        <v>45074</v>
+      </c>
+      <c r="D37" s="1" t="str">
+        <f>vlookup($B37,Holidays!$A:$I,2)</f>
+        <v>Spain</v>
+      </c>
+      <c r="E37" s="1" t="str">
+        <f>vlookup($B37,Holidays!$A:$I,3)</f>
+        <v>Murcia</v>
+      </c>
+      <c r="F37" s="1" t="str">
+        <f>vlookup($A37,Matchdays!$A:$G,4,false)</f>
+        <v>Saurines</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>156</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
       <c r="B1" s="1" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>137</v>
+        <v>164</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>140</v>
+        <v>167</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2">
@@ -13511,7 +13934,7 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C2" s="1">
         <v>4.0</v>
@@ -13526,16 +13949,16 @@
         <v>0.62</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="K2" s="1">
         <v>1.0</v>
@@ -13564,7 +13987,7 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1">
         <v>4.0</v>
@@ -13579,16 +14002,16 @@
         <v>0.59</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="K3" s="1">
         <v>2.0</v>
@@ -13617,7 +14040,7 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C4" s="1">
         <v>4.0</v>
@@ -13632,16 +14055,16 @@
         <v>0.56</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>149</v>
+        <v>176</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="K4" s="1">
         <v>0.0</v>
@@ -13670,7 +14093,7 @@
         <v>3.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1">
         <v>4.0</v>
@@ -13685,16 +14108,16 @@
         <v>0.56</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="K5" s="1">
         <v>11.0</v>
@@ -13723,7 +14146,7 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="C6" s="1">
         <v>4.0</v>
@@ -13738,16 +14161,16 @@
         <v>0.54</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>149</v>
+        <v>176</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="K6" s="1">
         <v>2.0</v>
@@ -13776,7 +14199,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C7" s="1">
         <v>4.0</v>
@@ -13791,16 +14214,16 @@
         <v>0.51</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>158</v>
+        <v>185</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="K7" s="1">
         <v>4.0</v>
@@ -13829,7 +14252,7 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1">
         <v>4.0</v>
@@ -13844,16 +14267,16 @@
         <v>0.45</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>160</v>
+        <v>187</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="K8" s="1">
         <v>3.0</v>
@@ -13882,7 +14305,7 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C9" s="1">
         <v>4.0</v>
@@ -13897,16 +14320,16 @@
         <v>0.47</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="K9" s="1">
         <v>10.0</v>
@@ -13935,7 +14358,7 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C10" s="1">
         <v>3.0</v>
@@ -13950,16 +14373,16 @@
         <v>0.48</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>160</v>
+        <v>187</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="K10" s="1">
         <v>2.0</v>
@@ -13988,7 +14411,7 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="C11" s="1">
         <v>4.0</v>
@@ -14003,16 +14426,16 @@
         <v>0.37</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>166</v>
+        <v>193</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="K11" s="1">
         <v>0.0</v>
@@ -14041,7 +14464,7 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C12" s="1">
         <v>4.0</v>
@@ -14056,16 +14479,16 @@
         <v>0.35</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>166</v>
+        <v>193</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="K12" s="1">
         <v>0.0</v>
@@ -14094,7 +14517,7 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C13" s="1">
         <v>2.0</v>
@@ -14109,16 +14532,16 @@
         <v>0.48</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="K13" s="1">
         <v>0.0</v>
@@ -14147,7 +14570,7 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C14" s="1">
         <v>1.0</v>
@@ -14162,16 +14585,16 @@
         <v>0.67</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>171</v>
+        <v>198</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="K14" s="1">
         <v>3.0</v>
@@ -14200,7 +14623,7 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C15" s="1">
         <v>2.0</v>
@@ -14215,16 +14638,16 @@
         <v>0.23</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="K15" s="1">
         <v>0.0</v>
@@ -14253,7 +14676,7 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C16" s="1">
         <v>1.0</v>
@@ -14268,16 +14691,16 @@
         <v>0.0</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="I16" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="J16" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>145</v>
       </c>
       <c r="K16" s="1">
         <v>1.0</v>
